--- a/Results_experiment/exp_1/eval_cycle_XII.xlsx
+++ b/Results_experiment/exp_1/eval_cycle_XII.xlsx
@@ -447,13 +447,13 @@
         <v>530</v>
       </c>
       <c r="D2">
-        <v>-6.416428263290683</v>
+        <v>0.4921049357710483</v>
       </c>
       <c r="E2">
-        <v>35.56370433959941</v>
+        <v>9.306718694224115</v>
       </c>
       <c r="F2">
-        <v>25.25858747020083</v>
+        <v>7.380145810150875</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -467,13 +467,13 @@
         <v>509</v>
       </c>
       <c r="D3">
-        <v>-41.19780935105478</v>
+        <v>0.5841636059015378</v>
       </c>
       <c r="E3">
-        <v>48.08102456519465</v>
+        <v>4.772984332797438</v>
       </c>
       <c r="F3">
-        <v>32.38595721782835</v>
+        <v>3.325800054214441</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -487,13 +487,13 @@
         <v>429</v>
       </c>
       <c r="D4">
-        <v>-55.07124841287617</v>
+        <v>0.5220842985900641</v>
       </c>
       <c r="E4">
-        <v>69.00520136676018</v>
+        <v>6.370703078271068</v>
       </c>
       <c r="F4">
-        <v>53.54887132831178</v>
+        <v>4.703079712366585</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -507,13 +507,13 @@
         <v>371</v>
       </c>
       <c r="D5">
-        <v>-22.04997030862646</v>
+        <v>0.4068530408822286</v>
       </c>
       <c r="E5">
-        <v>31.57768956271071</v>
+        <v>5.065546657506846</v>
       </c>
       <c r="F5">
-        <v>20.68728403174732</v>
+        <v>3.579121601469112</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -527,13 +527,13 @@
         <v>325</v>
       </c>
       <c r="D6">
-        <v>-15.86766219162371</v>
+        <v>0.08021204208747945</v>
       </c>
       <c r="E6">
-        <v>30.78103630677703</v>
+        <v>7.187860658671854</v>
       </c>
       <c r="F6">
-        <v>19.51137264950917</v>
+        <v>5.500631659053839</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -547,13 +547,13 @@
         <v>235</v>
       </c>
       <c r="D7">
-        <v>-85.59029100031091</v>
+        <v>-1.660248479606988</v>
       </c>
       <c r="E7">
-        <v>49.55803474678775</v>
+        <v>8.686415076416198</v>
       </c>
       <c r="F7">
-        <v>30.81331400253037</v>
+        <v>7.542585149439091</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -567,13 +567,13 @@
         <v>223</v>
       </c>
       <c r="D8">
-        <v>-1.367697556646574</v>
+        <v>0.5121358623857362</v>
       </c>
       <c r="E8">
-        <v>10.36345986817914</v>
+        <v>4.704257699021179</v>
       </c>
       <c r="F8">
-        <v>7.604864187371571</v>
+        <v>3.403191860113711</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -587,13 +587,13 @@
         <v>84</v>
       </c>
       <c r="D9">
-        <v>-39.98580345848196</v>
+        <v>0.5089429446898945</v>
       </c>
       <c r="E9">
-        <v>86.31279105220352</v>
+        <v>9.44766338970526</v>
       </c>
       <c r="F9">
-        <v>61.5542833336762</v>
+        <v>6.380270384429466</v>
       </c>
     </row>
   </sheetData>
